--- a/www/download/COUNTRY.AUS.zdW16.xlsx
+++ b/www/download/COUNTRY.AUS.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Austrália</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>1.71719217078341</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1.93185942742701</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>1.83856311956111</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1.53401523625088</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>1.35762763363416</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>1.30916783391584</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>1.32740425875999</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>1.19251906971883</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>1.16922824826264</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>1.2637368100773</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>1.08754876441077</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.968795117536151</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.9654373350979</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>1.03260235412685</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10779390006997</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>9.045</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>9.183</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>9.43</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>9.582</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>9.904</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>10.146</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>10.467</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>10.752</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>10.866</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>11.025</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>11.272</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>11.473</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>11.558</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>11.622</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>11.863</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>7.847</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7.942</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>8.209</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>8.387</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>8.67</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>8.936</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>9.288</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>9.556</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>9.668</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>9.778</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>10.039</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>10.304</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>10.415</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>10.454</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>10.669</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>16299.716</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>16335.968</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>16569.644</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>16822.948</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>17474.181</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>17968.639</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>18559.812</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>18932.143</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>18639.808</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>19470.337</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>19481.323</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>20027.955</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>20052.977</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>20298.753</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>20592.778</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>14013.16</t>
+          <t>18326219528.9142</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>14009.876</t>
+          <t>17753128937.7122</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14312.324</t>
+          <t>18641668864.7746</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14633.962</t>
+          <t>19927589229.177</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>15189.58</t>
+          <t>20856922799.6132</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>15732.532</t>
+          <t>21356429110.2241</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>16355.367</t>
+          <t>21929331422.7996</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>16687.979</t>
+          <t>23380087307.9387</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>16433.831</t>
+          <t>23413929280.9966</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>17148.781</t>
+          <t>23501164643.9457</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>17250.386</t>
+          <t>24323154290.2927</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>17886.616</t>
+          <t>27538905587.7985</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17957.596</t>
+          <t>27157590579.6992</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>18149.227</t>
+          <t>27314385598.2693</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>18445.658</t>
+          <t>26792798983.3068</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6843913050.21835</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6661491877.29695</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7488166954.958</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8902857028.47447</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10091648700.4429</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10630843826.0595</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>10456998325.0189</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>11048058417.9301</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>9716456774.68953</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>10170532699.2867</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>10897522031.332</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>12453990554.1947</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>12035822703.2128</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>12296014641.8406</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>12226764342.0043</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1497824.56925551</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1529692.19923308</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1467598.55119559</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1137095.59578256</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1004778.10781679</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>918874.524039087</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>899480.230454311</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>799990.486821367</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>769323.05754246</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>827554.098076391</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>679907.78357846</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>658165.853152577</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>632365.342130211</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>654275.951593205</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>684807.143811702</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>71399.911072785</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>70395.0795293189</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>70817.4775402454</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>79593.220002863</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>87410.9796640238</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>98464.4274813803</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>107651.572107012</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>126302.859329431</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>136076.7436179</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>127984.241643722</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>142554.439768415</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>156147.458110068</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>149349.406591591</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>153356.904045205</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>154369.356438715</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>166243.364398724</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>158686.532684341</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>167854.430990904</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>195348.994064941</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>225318.2009049</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>249190.770842704</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>270386.674865912</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>323376.995430295</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>353205.496073993</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>323995.612197441</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>370479.160079084</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>447237.87864779</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>430819.607843062</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>430794.490386772</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>424043.379833747</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.04753624091599</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.10311387569909</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.911325440002864</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.643737729719284</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.50516337328839</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.479894941306034</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.56405944532562</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.510489750209571</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.691339896947683</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.686124169405865</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.582964085817172</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.436215638848023</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.492012340395014</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.476025161700944</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.508629551044103</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.71719217078341</t>
+          <t>872.189155076839</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.93185942742701</t>
+          <t>838.786348686353</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.83856311956111</t>
+          <t>912.183018590674</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.53401523625088</t>
+          <t>1061.44371402228</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.35762763363416</t>
+          <t>1164.02219198625</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.30916783391584</t>
+          <t>1189.64993004894</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.32740425875999</t>
+          <t>1125.84696392379</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.19251906971883</t>
+          <t>1156.149274944</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.16922824826264</t>
+          <t>1005.00636112326</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.2637368100773</t>
+          <t>1040.17830599182</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.08754876441077</t>
+          <t>1085.4937027878</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.968795117536151</t>
+          <t>1208.68312972446</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.9654373350979</t>
+          <t>1155.57361770178</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.03260235412685</t>
+          <t>1176.15295727035</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1.10779390006997</t>
+          <t>1146.05745095154</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>9388822024.18663</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>8977071875.00546</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>9597906717.67199</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>11209985586.4704</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>13349034312.4742</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>14926320935.7932</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>14936651611.2385</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>15454216761.7551</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>16553167116.2388</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>15852793312.2762</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>19135807354.1698</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>21504475162.6765</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>20460675986.2218</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>20726847905.9195</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>19634212678.3898</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>8538708452.31393</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>8279707407.21335</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>8830087544.68573</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>10353065105.2509</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>12521445311.9989</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>13991419237.9245</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>13968644404.4861</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>14612162931.5079</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>15827767109.7124</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>15270655698.4536</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>18639328485.087</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>21154518837.8727</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>19962905470.7605</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>20344574255.7835</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>19025412954.802</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>850113571.8727</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>697364467.79211</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>767819172.986254</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.727</t>
+          <t>856920481.219551</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>827589000.47523</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.399</t>
+          <t>934901697.868716</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.573</t>
+          <t>968007206.752441</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.092</t>
+          <t>842053830.247179</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.326</t>
+          <t>725400006.526442</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.219</t>
+          <t>582137613.822595</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>3.927</t>
+          <t>496478869.082707</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>4.642</t>
+          <t>349956324.803754</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4.937</t>
+          <t>497770515.46125</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>4.903</t>
+          <t>382273650.136013</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>4.814</t>
+          <t>608799723.587763</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>1785.83890395373</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>1764.06320866924</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>1743.47860937096</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1744.73508071179</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1752.04356907257</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.484</t>
+          <t>1760.5569134045</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1760.89157791617</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.918</t>
+          <t>1746.35162951514</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.097</t>
+          <t>1699.80735525398</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.987</t>
+          <t>1753.86978222446</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.484</t>
+          <t>1718.29754689378</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2.931</t>
+          <t>1735.92961332204</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2.962</t>
+          <t>1724.13009784596</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.874</t>
+          <t>1736.03135894001</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2.724</t>
+          <t>1728.97613769976</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>1802.12896034297</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>1779.00364159733</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>1757.11839387558</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>1755.75705909863</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.623</t>
+          <t>1764.40708014264</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>1771.0796344153</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>1773.25694333456</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>1760.73519301317</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>1715.50312982827</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.955</t>
+          <t>1766.05303859946</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1728.33849623207</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.442</t>
+          <t>1745.70762646053</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1735.03536012102</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>1746.64313629963</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1735.88180243072</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>90960.7541794427</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80634.1193489764</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>82414.7534740801</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>95533.7553802665</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>122746.417941038</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>149389.25126695</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>162867.29361208</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>195184.604927593</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>242373.402434747</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>199410.200718784</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>273802.175157575</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>327102.433641638</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>312589.740080852</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>320236.370146185</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>287161.82244288</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3318574067.64045</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2942407659.81492</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2873026326.35415</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2609935333.2343</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2981878887.91398</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3074540349.54721</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3283496205.91359</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3551356716.3713</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3672175471.09669</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3298418883.10584</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3585099808.90843</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4386329630.14902</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>4040959524.39036</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>4220730705.8287</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>3935500432.30062</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>84265.0830625757</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>75171.7291136289</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>85369.739372719</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>102875.821409688</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>131913.441055619</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>152116.58981814</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>164170.613782858</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>205664.42478499</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>224651.859830714</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>194747.134250034</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>242486.693902192</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>309969.309734211</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>311548.862326707</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>308247.433243131</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>288989.970711748</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16299.716</t>
+          <t>11791730326.3111</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16335.968</t>
+          <t>11142012754.1779</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16569.644</t>
+          <t>12894171352.5916</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16822.948</t>
+          <t>14811171542.1788</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>17474.181</t>
+          <t>17458675566.7902</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17968.639</t>
+          <t>18305175452.4996</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>18559.812</t>
+          <t>18352127023.2145</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>18932.143</t>
+          <t>19915551309.1384</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>18639.808</t>
+          <t>18881893696.9994</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>19470.337</t>
+          <t>18754144107.218</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>19481.323</t>
+          <t>20343827149.2367</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>20027.955</t>
+          <t>24659605237.7517</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>20052.977</t>
+          <t>24426338943.0544</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>20298.753</t>
+          <t>24071657821.0851</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>20592.778</t>
+          <t>23701996218.0653</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14013.16</t>
+          <t>6695.67111686705</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14009.876</t>
+          <t>5462.39023534746</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>14312.324</t>
+          <t>-2954.98589863892</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>14633.962</t>
+          <t>-7342.06602942172</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15189.58</t>
+          <t>-9167.02311458174</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15732.532</t>
+          <t>-2727.3385511894</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>16355.367</t>
+          <t>-1303.32017077733</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>16687.979</t>
+          <t>-10479.8198573971</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>16433.831</t>
+          <t>17721.5426040333</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17148.781</t>
+          <t>4663.06646874934</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>17250.386</t>
+          <t>31315.4812553834</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>17886.616</t>
+          <t>17133.1239074271</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>17957.596</t>
+          <t>1040.8777541445</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>18149.227</t>
+          <t>11988.9369030546</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>18445.658</t>
+          <t>-1828.14826886819</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>21610.99</t>
+          <t>-8473156258.67066</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20797.768</t>
+          <t>-8199605094.36301</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21990.447</t>
+          <t>-10021145026.2375</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>23645.123</t>
+          <t>-12201236208.9445</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>25064.774</t>
+          <t>-14476796678.8762</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>26052.099</t>
+          <t>-15230635102.9524</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>26768.507</t>
+          <t>-15068630817.3009</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>28572.485</t>
+          <t>-16364194592.7671</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>28808.141</t>
+          <t>-15209718225.9027</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>29000.507</t>
+          <t>-15455725224.1122</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>30078.4</t>
+          <t>-16758727340.3282</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>34460.538</t>
+          <t>-20273275607.6027</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>34146.365</t>
+          <t>-20385379418.664</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>34223.998</t>
+          <t>-19850927115.2564</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>26792.799</t>
+          <t>-19766495785.7647</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>160582.862507636</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>153585.680271444</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>168899.064137578</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>219538.905124182</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>269049.391956048</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>309061.206964675</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>329304.031231776</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>397316.764994566</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>451223.70516446</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>417849.109155417</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>547155.471638239</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>646460.300009009</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>647235.111716264</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>630973.769715</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>584025.992249869</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7870.933</t>
+          <t>0.117160325709481</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7875.482</t>
+          <t>0.121673701361311</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>7864.886</t>
+          <t>0.121011747781996</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8119.32</t>
+          <t>0.121350119119503</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8091.331</t>
+          <t>0.120098087278065</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8438.71</t>
+          <t>0.122534764091771</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>8730.93</t>
+          <t>0.123502298627233</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>9131.67</t>
+          <t>0.123508950221656</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>9020.503</t>
+          <t>0.1322474309429</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>9283.393</t>
+          <t>0.127206734188004</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>9359.16</t>
+          <t>0.132866331249043</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>9614.861</t>
+          <t>0.133950296433824</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>9414.544</t>
+          <t>0.127518851974122</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>9723.545</t>
+          <t>0.124854236021116</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>9753.689</t>
+          <t>0.119131008098338</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>200799.080129438</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>187877.810512451</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>208739.334745531</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>267846.185293633</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>325683.950314428</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>362665.544935247</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>390912.181910073</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>474412.656057536</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>505430.862505818</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>487797.830144797</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>615284.235602794</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>739406.376609815</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>766015.670376561</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>740637.890223183</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>706818.003549762</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7764.503</t>
+          <t>228286.287730193</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7503.799</t>
+          <t>214270.60066356</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8457.233</t>
+          <t>236988.459468206</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>10040.125</t>
+          <t>302836.18414442</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>11367.001</t>
+          <t>368526.444018213</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>12068.206</t>
+          <t>407347.068764064</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>11916.569</t>
+          <t>436920.442335109</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>12531.276</t>
+          <t>530545.704777409</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11151.936</t>
+          <t>565215.179243737</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>11692.191</t>
+          <t>545246.627971203</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>12504.397</t>
+          <t>687978.518613445</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>14349.03</t>
+          <t>820086.46542994</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>13906.06</t>
+          <t>848243.279663591</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>14096.14</t>
+          <t>820453.507213221</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>12226.764</t>
+          <t>783655.533317229</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>80.48</t>
+          <t>1253196.36408681</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>1172460.03416428</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>1323766.35526373</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>1727132.11316263</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>2122536.36206987</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>2399001.02984087</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>2572834.15442542</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>3092050.26927516</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>3326029.84298293</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>3218631.36744093</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>3927046.85311161</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>4641830.82241605</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>4937348.89207421</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>4902934.79359827</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>50.86</t>
+          <t>4813985.77263268</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.777</t>
+          <t>329886.331438636</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.802</t>
+          <t>339328.232611844</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.742</t>
+          <t>347127.777935365</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>356272.599949731</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.225</t>
+          <t>368857.328059082</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.142</t>
+          <t>378110.769654716</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>393135.129032121</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>412979.268868071</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>413853.164277654</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.039</t>
+          <t>422141.929151405</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>435717.207841987</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>451196.207845602</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>463503.035391403</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>476298.521455719</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>488424.001292229</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>290480.621771382</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>298630.484672896</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>306135.870367973</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>315541.327742394</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>326422.681052237</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>336357.858407728</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>351934.464245832</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>369571.279470455</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>369739.556825768</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>377880.993998097</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>389677.761669055</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>406940.617805633</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>419133.338736686</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>430432.256438619</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>442129.878410539</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>146824.894194348</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>142657.552054977</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>160191.280305467</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>209587.687667404</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>254912.557262734</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>293961.025247468</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>317750.932058192</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>381895.882790765</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>439858.901973912</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>409431.584807229</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>521772.308016041</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>621774.614658291</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>629605.062513007</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>612152.17791606</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>573494.97806479</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>14013160000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>14009876000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>14312324000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>14633962000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15189580000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>15732532000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>16355367000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>16687979000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>16433831000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>17148781000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>17250386000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>17886616000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>17957596000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>18149227000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>18445658000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>16299715807.6141</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16335967789.5137</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>16569644025.4306</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>16822947791.403</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>17474181336.9007</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>17968638972.7294</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>18559811529.9806</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>18932143175.2364</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>18639807834.6647</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>19470337388.6254</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>19481323398.01</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>20027955446.187</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>20052976540.8221</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>20298752939.957</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>20592777973.4083</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>7870933371.67118</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7875481947.48491</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>7864886010.7566</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>8119319995.66525</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>8091330604.31539</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>8438709661.17067</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>8730929525.61658</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>9131669599.54924</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>9020503042.20175</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>9283393420.97856</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>9359159723.08198</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>9614861155.47545</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>9414543729.43245</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>9723544995.86734</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>9753688733.13505</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9044700</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9182650</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9430010</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9581592</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9903713</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>10145585</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>10466510</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10752408</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10865505</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>11024775</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>11271706</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>11472686</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>11557676</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>11621580</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>11863007</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>7846822</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7941822</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>8209062</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>8387498</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>8669636</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>8936111</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>9288117</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>9555910</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>9668055</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>9777682</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>10039231</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>10303768</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>10415453</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>10454435</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>10668544</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>16299715807.6141</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16335967789.5137</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>16569644025.4306</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>16822947791.403</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17474181336.9007</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>17968638972.7294</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>18559811529.9806</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>18932143175.2364</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>18639807834.6647</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>19470337388.6254</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>19481323398.01</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>20027955446.187</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>20052976540.8221</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>20298752939.957</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>20592777973.4083</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>14013160000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>14009876000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>14312324000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>14633962000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>15189580000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>15732532000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>16355367000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>16687979000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>16433831000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>17148781000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>17250386000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>17886616000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>17957596000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>18149227000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>18445658000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>795738.228276079</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>758249.740972326</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>846925.503179066</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1100133.62665529</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1329886.73772367</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1484266.35382978</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1588225.32534999</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1917733.661974</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2097357.72144838</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1986523.01527065</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2484151.78350897</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2931207.75149672</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2962485.3652</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2874155.75622</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2723737.21668623</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>375111.187748</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>356928.13926</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>397179.72672</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>512423.848344</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>623438.992442</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>701308.09172</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>754671.3759</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>912441.578344</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1005074.072665</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>954678.206448</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1209750.812837</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1441861.11828</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1477848.366</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1432605.682224</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1357150.478885</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2034554.32763078</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2063353.28646763</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2154409.54676415</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2296346.40846903</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2356370.38759262</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2409789.54009451</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2450544.53316309</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2470545.7346295</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2456312.55007797</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2532719.52057855</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2487115.32841186</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2526356.41163929</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2702906.51535235</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2830073.37352695</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>3149125.36308419</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
